--- a/Fase 2/Evidencias/docs/Plan_de_Pruebas_Bomberos_completado.xlsx
+++ b/Fase 2/Evidencias/docs/Plan_de_Pruebas_Bomberos_completado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patof\Documents\GitHub\proyecto-capstone\Fase 2\Evidencias\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED12E2C-05C5-4B6C-BCCA-5D132A465F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C7D19A-DCBB-40F3-8E3C-DBC0E58E9B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="56">
+  <futureMetadata name="XLRICHVALUE" count="54">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -426,22 +426,8 @@
         </ext>
       </extLst>
     </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="54"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="55"/>
-        </ext>
-      </extLst>
-    </bk>
   </futureMetadata>
-  <valueMetadata count="56">
+  <valueMetadata count="54">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -603,12 +589,6 @@
     </bk>
     <bk>
       <rc t="1" v="53"/>
-    </bk>
-    <bk>
-      <rc t="1" v="54"/>
-    </bk>
-    <bk>
-      <rc t="1" v="55"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2217,35 +2197,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2255,10 +2206,39 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3337,7 +3317,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="56">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="54">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -3554,14 +3534,6 @@
     <v>53</v>
     <v>5</v>
   </rv>
-  <rv s="0">
-    <v>54</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>55</v>
-    <v>5</v>
-  </rv>
 </rvData>
 </file>
 
@@ -3630,8 +3602,6 @@
   <rel r:id="rId52"/>
   <rel r:id="rId53"/>
   <rel r:id="rId54"/>
-  <rel r:id="rId55"/>
-  <rel r:id="rId56"/>
 </richValueRels>
 </file>
 
@@ -11684,7 +11654,7 @@
       <c r="AB7" s="15"/>
       <c r="AC7" s="15"/>
     </row>
-    <row r="8" spans="5:29" ht="120.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="5:29" ht="120" x14ac:dyDescent="0.25">
       <c r="E8" s="14" t="s">
         <v>20</v>
       </c>
@@ -12075,9 +12045,7 @@
       <c r="Y13" s="12" t="e" vm="20">
         <v>#VALUE!</v>
       </c>
-      <c r="Z13" s="12" t="e" vm="21">
-        <v>#VALUE!</v>
-      </c>
+      <c r="Z13" s="12"/>
       <c r="AA13" s="12"/>
       <c r="AB13" s="12"/>
       <c r="AC13" s="12"/>
@@ -12135,10 +12103,10 @@
       <c r="U14" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="V14" s="14" t="e" vm="22">
+      <c r="V14" s="14" t="e" vm="21">
         <v>#VALUE!</v>
       </c>
-      <c r="W14" s="12" t="e" vm="23">
+      <c r="W14" s="12" t="e" vm="22">
         <v>#VALUE!</v>
       </c>
       <c r="X14" s="12"/>
@@ -12201,7 +12169,7 @@
       <c r="U15" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="V15" s="14" t="e" vm="24">
+      <c r="V15" s="14" t="e" vm="23">
         <v>#VALUE!</v>
       </c>
       <c r="W15" s="12"/>
@@ -12265,7 +12233,7 @@
       <c r="U16" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="V16" s="14" t="e" vm="25">
+      <c r="V16" s="14" t="e" vm="24">
         <v>#VALUE!</v>
       </c>
       <c r="W16" s="12"/>
@@ -12329,27 +12297,25 @@
       <c r="U17" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="V17" s="14" t="e" vm="26">
+      <c r="V17" s="14" t="e" vm="25">
         <v>#VALUE!</v>
       </c>
-      <c r="W17" s="12" t="e" vm="27">
+      <c r="W17" s="12" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
-      <c r="X17" s="12" t="e" vm="28">
+      <c r="X17" s="12" t="e" vm="27">
         <v>#VALUE!</v>
       </c>
-      <c r="Y17" s="12" t="e" vm="29">
+      <c r="Y17" s="12" t="e" vm="28">
         <v>#VALUE!</v>
       </c>
-      <c r="Z17" s="12" t="e" vm="30">
+      <c r="Z17" s="12" t="e" vm="29">
         <v>#VALUE!</v>
       </c>
-      <c r="AA17" s="12" t="e" vm="31">
+      <c r="AA17" s="12" t="e" vm="30">
         <v>#VALUE!</v>
       </c>
-      <c r="AB17" s="12" t="e" vm="32">
-        <v>#VALUE!</v>
-      </c>
+      <c r="AB17" s="12"/>
       <c r="AC17" s="12"/>
     </row>
     <row r="18" spans="5:29" ht="117" customHeight="1" x14ac:dyDescent="0.25">
@@ -12405,16 +12371,16 @@
       <c r="U18" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="V18" s="14" t="e" vm="33">
+      <c r="V18" s="14" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
-      <c r="W18" s="12" t="e" vm="34">
+      <c r="W18" s="12" t="e" vm="32">
         <v>#VALUE!</v>
       </c>
-      <c r="X18" s="12" t="e" vm="35">
+      <c r="X18" s="12" t="e" vm="33">
         <v>#VALUE!</v>
       </c>
-      <c r="Y18" s="12" t="e" vm="36">
+      <c r="Y18" s="12" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
       <c r="Z18" s="12"/>
@@ -12475,10 +12441,10 @@
       <c r="U19" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="V19" s="14" t="e" vm="37">
+      <c r="V19" s="14" t="e" vm="35">
         <v>#VALUE!</v>
       </c>
-      <c r="W19" s="12" t="e" vm="38">
+      <c r="W19" s="12" t="e" vm="36">
         <v>#VALUE!</v>
       </c>
       <c r="X19" s="12"/>
@@ -12541,10 +12507,10 @@
       <c r="U20" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="V20" s="14" t="e" vm="39">
+      <c r="V20" s="14" t="e" vm="37">
         <v>#VALUE!</v>
       </c>
-      <c r="W20" s="12" t="e" vm="40">
+      <c r="W20" s="12" t="e" vm="38">
         <v>#VALUE!</v>
       </c>
       <c r="X20" s="12"/>
@@ -12607,7 +12573,7 @@
       <c r="U21" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="V21" s="12" t="e" vm="41">
+      <c r="V21" s="12" t="e" vm="39">
         <v>#VALUE!</v>
       </c>
       <c r="X21" s="12"/>
@@ -12670,13 +12636,13 @@
       <c r="U22" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="V22" s="14" t="e" vm="42">
+      <c r="V22" s="14" t="e" vm="40">
         <v>#VALUE!</v>
       </c>
-      <c r="W22" s="12" t="e" vm="43">
+      <c r="W22" s="12" t="e" vm="41">
         <v>#VALUE!</v>
       </c>
-      <c r="X22" s="12" t="e" vm="44">
+      <c r="X22" s="12" t="e" vm="42">
         <v>#VALUE!</v>
       </c>
       <c r="Y22" s="12"/>
@@ -12738,25 +12704,25 @@
       <c r="U23" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="V23" s="14" t="e" vm="45">
+      <c r="V23" s="14" t="e" vm="43">
         <v>#VALUE!</v>
       </c>
-      <c r="W23" s="12" t="e" vm="46">
+      <c r="W23" s="12" t="e" vm="44">
         <v>#VALUE!</v>
       </c>
-      <c r="X23" s="12" t="e" vm="47">
+      <c r="X23" s="12" t="e" vm="45">
         <v>#VALUE!</v>
       </c>
-      <c r="Y23" s="12" t="e" vm="48">
+      <c r="Y23" s="12" t="e" vm="46">
         <v>#VALUE!</v>
       </c>
-      <c r="Z23" s="12" t="e" vm="49">
+      <c r="Z23" s="12" t="e" vm="47">
         <v>#VALUE!</v>
       </c>
-      <c r="AA23" s="12" t="e" vm="50">
+      <c r="AA23" s="12" t="e" vm="48">
         <v>#VALUE!</v>
       </c>
-      <c r="AB23" s="12" t="e" vm="51">
+      <c r="AB23" s="12" t="e" vm="49">
         <v>#VALUE!</v>
       </c>
       <c r="AC23" s="12"/>
@@ -12814,19 +12780,19 @@
       <c r="U24" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="V24" s="14" t="e" vm="52">
+      <c r="V24" s="14" t="e" vm="50">
         <v>#VALUE!</v>
       </c>
-      <c r="W24" s="12" t="e" vm="53">
+      <c r="W24" s="12" t="e" vm="51">
         <v>#VALUE!</v>
       </c>
-      <c r="X24" s="12" t="e" vm="54">
+      <c r="X24" s="12" t="e" vm="52">
         <v>#VALUE!</v>
       </c>
-      <c r="Y24" s="12" t="e" vm="55">
+      <c r="Y24" s="12" t="e" vm="53">
         <v>#VALUE!</v>
       </c>
-      <c r="Z24" s="12" t="e" vm="56">
+      <c r="Z24" s="12" t="e" vm="54">
         <v>#VALUE!</v>
       </c>
       <c r="AA24" s="12"/>
@@ -33527,7 +33493,7 @@
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="58" t="s">
         <v>318</v>
       </c>
       <c r="C6" s="25" t="s">
@@ -33547,7 +33513,7 @@
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
-      <c r="O6" s="59" t="s">
+      <c r="O6" s="42" t="s">
         <v>354</v>
       </c>
       <c r="P6" s="25" t="s">
@@ -33562,7 +33528,7 @@
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="B7" s="45"/>
+      <c r="B7" s="59"/>
       <c r="C7" s="25" t="s">
         <v>320</v>
       </c>
@@ -33580,7 +33546,7 @@
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
-      <c r="O7" s="60"/>
+      <c r="O7" s="43"/>
       <c r="P7" s="25" t="s">
         <v>320</v>
       </c>
@@ -33593,7 +33559,7 @@
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
-      <c r="B8" s="45"/>
+      <c r="B8" s="59"/>
       <c r="C8" s="25" t="s">
         <v>32</v>
       </c>
@@ -33611,7 +33577,7 @@
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
-      <c r="O8" s="60"/>
+      <c r="O8" s="43"/>
       <c r="P8" s="25" t="s">
         <v>32</v>
       </c>
@@ -33624,7 +33590,7 @@
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="45"/>
+      <c r="B9" s="59"/>
       <c r="C9" s="25" t="s">
         <v>321</v>
       </c>
@@ -33642,7 +33608,7 @@
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
-      <c r="O9" s="60"/>
+      <c r="O9" s="43"/>
       <c r="P9" s="25" t="s">
         <v>321</v>
       </c>
@@ -33655,7 +33621,7 @@
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="46"/>
+      <c r="B10" s="52"/>
       <c r="C10" s="25" t="s">
         <v>322</v>
       </c>
@@ -33673,7 +33639,7 @@
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
-      <c r="O10" s="61"/>
+      <c r="O10" s="44"/>
       <c r="P10" s="25" t="s">
         <v>322</v>
       </c>
@@ -33707,8 +33673,8 @@
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="43"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="57"/>
       <c r="D12" s="29"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -33728,10 +33694,10 @@
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="45" t="s">
         <v>323</v>
       </c>
-      <c r="C13" s="52"/>
+      <c r="C13" s="46"/>
       <c r="D13" s="30">
         <f>COUNTIF('Plan de prueba'!$E$2:$E$500,"*")</f>
         <v>48</v>
@@ -33746,10 +33712,10 @@
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
-      <c r="O13" s="58" t="s">
+      <c r="O13" s="45" t="s">
         <v>323</v>
       </c>
-      <c r="P13" s="52"/>
+      <c r="P13" s="46"/>
       <c r="Q13" s="30">
         <f>COUNTIF('Plan de prueba'!H2:H26,'Plan de prueba'!H26)</f>
         <v>25</v>
@@ -33763,7 +33729,7 @@
         <v>324</v>
       </c>
       <c r="C14" s="48"/>
-      <c r="D14" s="53">
+      <c r="D14" s="51">
         <f>SUM(D6+D7+D9+D10)/D13</f>
         <v>0.5</v>
       </c>
@@ -33781,7 +33747,7 @@
         <v>324</v>
       </c>
       <c r="P14" s="48"/>
-      <c r="Q14" s="53">
+      <c r="Q14" s="51">
         <f>SUM(Q6+Q7+Q9+Q10)/Q13</f>
         <v>0.96</v>
       </c>
@@ -33792,7 +33758,7 @@
       <c r="A15" s="1"/>
       <c r="B15" s="49"/>
       <c r="C15" s="50"/>
-      <c r="D15" s="46"/>
+      <c r="D15" s="52"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -33805,7 +33771,7 @@
       <c r="N15" s="1"/>
       <c r="O15" s="49"/>
       <c r="P15" s="50"/>
-      <c r="Q15" s="46"/>
+      <c r="Q15" s="52"/>
       <c r="R15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
@@ -33856,14 +33822,14 @@
     </row>
     <row r="18" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="54" t="s">
+      <c r="B18" s="60" t="s">
         <v>325</v>
       </c>
-      <c r="C18" s="55"/>
-      <c r="D18" s="51" t="s">
+      <c r="C18" s="61"/>
+      <c r="D18" s="55" t="s">
         <v>326</v>
       </c>
-      <c r="E18" s="52"/>
+      <c r="E18" s="46"/>
       <c r="F18" s="30">
         <f>COUNTIF('Plan de prueba'!$U$2:$U$500,D18)</f>
         <v>24</v>
@@ -33890,12 +33856,12 @@
     </row>
     <row r="19" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="56"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="51" t="s">
+      <c r="B19" s="62"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="55" t="s">
         <v>327</v>
       </c>
-      <c r="E19" s="52"/>
+      <c r="E19" s="46"/>
       <c r="F19" s="30">
         <f>COUNTIF('Plan de prueba'!$U$2:$U$500,D19)</f>
         <v>0</v>
@@ -33922,12 +33888,12 @@
     </row>
     <row r="20" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="56"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="51" t="s">
+      <c r="B20" s="62"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="55" t="s">
         <v>328</v>
       </c>
-      <c r="E20" s="52"/>
+      <c r="E20" s="46"/>
       <c r="F20" s="30">
         <f>COUNTIF('Plan de prueba'!$U$2:$U$500,D20)</f>
         <v>0</v>
@@ -33955,9 +33921,9 @@
     <row r="21" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="49"/>
-      <c r="C21" s="57"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="52"/>
+      <c r="C21" s="63"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="46"/>
       <c r="F21" s="37"/>
       <c r="G21" s="27"/>
       <c r="H21" s="27"/>
@@ -34008,10 +33974,10 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="32"/>
-      <c r="D23" s="62" t="s">
+      <c r="D23" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="E23" s="63"/>
+      <c r="E23" s="54"/>
       <c r="F23" s="34">
         <f>SUM(F18:F21)</f>
         <v>24</v>
@@ -40397,12 +40363,6 @@
     <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O6:O10"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="O14:P15"/>
-    <mergeCell ref="Q14:Q15"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D21:E21"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B6:B10"/>
     <mergeCell ref="B14:C15"/>
@@ -40412,6 +40372,12 @@
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D19:E19"/>
+    <mergeCell ref="O6:O10"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="O14:P15"/>
+    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D21:E21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
